--- a/progSpros_back/templates/Сравнительные таблицы.xlsx
+++ b/progSpros_back/templates/Сравнительные таблицы.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="19">
   <si>
     <t xml:space="preserve">Потребитель</t>
   </si>
@@ -254,6 +254,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
@@ -270,19 +274,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -493,12 +493,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="44.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="51" min="5" style="1" width="27.22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -511,24 +513,31 @@
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="D1" s="3" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="2" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="5"/>
-    </row>
-    <row r="4" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="C2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="8"/>
+    </row>
+    <row r="4" s="10" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
@@ -551,7 +560,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="36.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="5" style="1" width="27.22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -564,34 +574,34 @@
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="10"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="8"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -629,108 +639,108 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="9" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" s="11" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" s="12" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/progSpros_back/templates/Сравнительные таблицы.xlsx
+++ b/progSpros_back/templates/Сравнительные таблицы.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="19">
   <si>
     <t xml:space="preserve">Потребитель</t>
   </si>
@@ -554,14 +554,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="36.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="5" style="1" width="27.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="3" style="1" width="27.22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -574,9 +572,6 @@
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>0</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
@@ -587,16 +582,12 @@
       </c>
       <c r="C2" s="4" t="s">
         <v>0</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
       <c r="B3" s="7"/>
       <c r="C3" s="6"/>
-      <c r="D3" s="8"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10"/>
